--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486681_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486681_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4999</v>
+        <v>8.4061</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8339</v>
+        <v>7.8891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.666</v>
+        <v>0.517</v>
       </c>
       <c r="G2" t="n">
         <v>1.8771</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3146</v>
+        <v>0.2208</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3314</v>
+        <v>-0.2763</v>
       </c>
       <c r="U2" t="n">
-        <v>0.646</v>
+        <v>0.4971</v>
       </c>
       <c r="V2" t="n">
         <v>7.0805</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6839</v>
+        <v>4.2661</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3842</v>
+        <v>4.8671</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7003</v>
+        <v>-0.6009</v>
       </c>
       <c r="G3" t="n">
         <v>0.2939</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1969</v>
+        <v>0.7791</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7995</v>
+        <v>0.2824</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3974</v>
+        <v>0.4968</v>
       </c>
       <c r="V3" t="n">
         <v>1.8415</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5251</v>
+        <v>2.757</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1515</v>
+        <v>2.4827</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3736</v>
+        <v>0.2743</v>
       </c>
       <c r="G4" t="n">
         <v>0.6468</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3956</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7716</v>
+        <v>0.1028</v>
       </c>
       <c r="U4" t="n">
-        <v>0.624</v>
+        <v>0.5246</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0273</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8531</v>
+        <v>2.3704</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2315</v>
+        <v>-0.59</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0846</v>
+        <v>2.9604</v>
       </c>
       <c r="G5" t="n">
         <v>2.5276</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0205</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5512</v>
+        <v>0.1927</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4693</v>
+        <v>0.3451</v>
       </c>
       <c r="V5" t="n">
         <v>0.6565</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0592</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4147</v>
+        <v>-1.8424</v>
       </c>
       <c r="F6" t="n">
-        <v>2.474</v>
+        <v>2.3995</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3807</v>
@@ -922,13 +922,13 @@
         <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2814</v>
+        <v>0.7792</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5518</v>
+        <v>0.0205</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.7588</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. ELTING</t>
+          <t>M. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2195</v>
+        <v>-2.021</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9324</v>
+        <v>-2.3849</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2871</v>
+        <v>0.3639</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1657</v>
+        <v>-5.0688</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7588</v>
+        <v>-0.7103</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4069</v>
+        <v>-4.3584</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-2.0328</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.5303</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1657</v>
+        <v>-3.036</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7588</v>
+        <v>-0.2079</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4069</v>
+        <v>-2.8282</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1239</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3973</v>
+        <v>-0.1034</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2759</v>
+        <v>-0.3522</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1213</v>
+        <v>0.2487</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6565</v>
+        <v>1.0273</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.0273</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. YOUNG MEDIERO</t>
+          <t>B. ELTING</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6456</v>
+        <v>-2.1946</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1089</v>
+        <v>-0.9324</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4632</v>
+        <v>-1.2622</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.0688</v>
+        <v>-1.1657</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7103</v>
+        <v>-0.7588</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.3584</v>
+        <v>-0.4069</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0328</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5024999999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5303</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.036</v>
+        <v>-1.1657</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2079</v>
+        <v>-0.7588</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.8282</v>
+        <v>-0.4069</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1239</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.728</v>
+        <v>-0.3724</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0761</v>
+        <v>-0.2759</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3481</v>
+        <v>-0.0965</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0273</v>
+        <v>-0.6565</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X9" t="n">
-        <v>1.0273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5897</v>
+        <v>-3.0202</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3615</v>
+        <v>-0.1566</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2282</v>
+        <v>-2.8635</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9482</v>
+        <v>2.7354</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3726</v>
+        <v>-0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3208</v>
+        <v>3.5153</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1477</v>
+        <v>3.9368</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9591</v>
+        <v>-0.5032</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1068</v>
+        <v>4.44</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8005</v>
+        <v>-1.2014</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5865</v>
+        <v>-0.2767</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.214</v>
+        <v>-0.9247</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5792</v>
+        <v>-2.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1048</v>
+        <v>-0.4619</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2484</v>
+        <v>-0.5175</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1435</v>
+        <v>0.0555</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0426</v>
+        <v>-2.7836</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0426</v>
+        <v>-3.0692</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8823</v>
+        <v>-3.5608</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5221</v>
+        <v>-1.2581</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3602</v>
+        <v>-2.3027</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7354</v>
+        <v>-2.9482</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.78</v>
+        <v>0.3726</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5153</v>
+        <v>-3.3208</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9368</v>
+        <v>-0.1477</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5032</v>
+        <v>1.9591</v>
       </c>
       <c r="L11" t="n">
-        <v>4.44</v>
+        <v>-2.1068</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2014</v>
+        <v>-2.8005</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2767</v>
+        <v>-1.5865</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9247</v>
+        <v>-1.214</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.51</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.324</v>
+        <v>-0.0759</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8829</v>
+        <v>-0.145</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4411</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7836</v>
+        <v>0.0426</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0692</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.7916</v>
+        <v>7.067499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>7.798500000000002</v>
+        <v>8.0745</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0069</v>
+        <v>-1.0067</v>
       </c>
       <c r="G12" t="n">
         <v>-2.689500000000001</v>
@@ -1390,10 +1390,10 @@
         <v>12.5501</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6549</v>
+        <v>1.930799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2442</v>
+        <v>-0.9685</v>
       </c>
       <c r="U12" t="n">
         <v>2.8991</v>
@@ -1405,7 +1405,7 @@
         <v>6.8248</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9293</v>
+        <v>-0.9293000000000002</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8683</v>
+        <v>4.8779</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5065</v>
+        <v>5.4031</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6383</v>
+        <v>-0.5252</v>
       </c>
       <c r="G13" t="n">
         <v>3.071</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>0.342</v>
+        <v>0.3516</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0555</v>
+        <v>-0.159</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3975</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.8415</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2842</v>
+        <v>3.5793</v>
       </c>
       <c r="E14" t="n">
-        <v>3.994</v>
+        <v>4.2009</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7098</v>
+        <v>-0.6216</v>
       </c>
       <c r="G14" t="n">
         <v>1.2621</v>
@@ -1546,13 +1546,13 @@
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3641</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8002</v>
+        <v>-0.5934</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4361</v>
+        <v>0.5243</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4804</v>
+        <v>1.9286</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8817</v>
+        <v>2.192</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4013</v>
+        <v>-0.2634</v>
       </c>
       <c r="G15" t="n">
         <v>1.9049</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7447</v>
+        <v>-0.2965</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0209</v>
+        <v>-0.7107</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2763</v>
+        <v>0.4142</v>
       </c>
       <c r="V15" t="n">
         <v>0.8995</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.183</v>
+        <v>-0.1581</v>
       </c>
       <c r="E16" t="n">
         <v>0.1378</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3208</v>
+        <v>-0.296</v>
       </c>
       <c r="G16" t="n">
         <v>0.8528</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6481</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4691</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2038</v>
+        <v>-0.179</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9421</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.345</v>
+        <v>-1.1326</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9542</v>
+        <v>-1.2563</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2992</v>
+        <v>0.1238</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8841</v>
+        <v>-1.7532</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3382</v>
+        <v>-0.8828</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2223</v>
+        <v>-0.8704</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0303</v>
+        <v>-1.2148</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1109</v>
+        <v>-0.6067</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9194</v>
+        <v>-0.6081</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1462</v>
+        <v>-0.5384</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4491</v>
+        <v>-0.2761</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3029</v>
+        <v>-0.2623</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0332</v>
+        <v>-0.1517</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1107</v>
+        <v>-0.0415</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1439</v>
+        <v>-0.1102</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARRO</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4345</v>
+        <v>-1.4058</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0346</v>
+        <v>0.9542</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6001</v>
+        <v>-2.3599</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8015</v>
+        <v>0.8841</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.1029</v>
+        <v>-1.3382</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3013</v>
+        <v>2.2223</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5516</v>
+        <v>2.0303</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4469</v>
+        <v>0.1109</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9985</v>
+        <v>1.9194</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3531</v>
+        <v>-1.1462</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.656</v>
+        <v>-1.4491</v>
       </c>
       <c r="O18" t="n">
         <v>0.3029</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.51</v>
+        <v>0.1931</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6067</v>
+        <v>-0.0275</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6615</v>
+        <v>-0.1107</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0548</v>
+        <v>0.0832</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2703</v>
+        <v>-2.4554</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6565</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>D. GARCIA NAVARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4884</v>
+        <v>-1.8275</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4632</v>
+        <v>-2.5518</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0252</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7532</v>
+        <v>-0.8015</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8828</v>
+        <v>-3.1029</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8704</v>
+        <v>2.3013</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2148</v>
+        <v>0.5516</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6067</v>
+        <v>-1.4469</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6081</v>
+        <v>1.9985</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5384</v>
+        <v>-1.3531</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2761</v>
+        <v>-1.656</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2623</v>
+        <v>0.3029</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7723</v>
+        <v>-2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.2138</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2484</v>
+        <v>0.1444</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2592</v>
+        <v>0.0694</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.2703</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5067</v>
+        <v>-2.7135</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5278</v>
+        <v>-1.7346</v>
       </c>
       <c r="F20" t="n">
         <v>-0.9789</v>
@@ -2014,10 +2014,10 @@
         <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7447</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4686</v>
+        <v>0.2618</v>
       </c>
       <c r="U20" t="n">
         <v>0.276</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.342</v>
+        <v>-3.3131</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5384</v>
+        <v>-2.435</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8036</v>
+        <v>-0.8781</v>
       </c>
       <c r="G21" t="n">
         <v>1.5778</v>
@@ -2092,13 +2092,13 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5184</v>
+        <v>-0.4895</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1438</v>
+        <v>0.0693</v>
       </c>
       <c r="V21" t="n">
         <v>-2.0845</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1249</v>
+        <v>-5.9373</v>
       </c>
       <c r="E22" t="n">
         <v>-3.9034</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2215</v>
+        <v>-2.034</v>
       </c>
       <c r="G22" t="n">
         <v>-4.5245</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5738</v>
+        <v>-0.3862</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6622</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.276</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7989</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.791600000000001</v>
+        <v>-6.102099999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>1.006799999999999</v>
+        <v>1.006899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.7985</v>
+        <v>-7.108999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>2.6896</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.516500000000002</v>
+        <v>-5.516500000000001</v>
       </c>
       <c r="I23" t="n">
         <v>8.206099999999999</v>
@@ -2239,7 +2239,7 @@
         <v>-3.1768</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9307</v>
+        <v>-1.930699999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.5502</v>
@@ -2248,13 +2248,13 @@
         <v>10.6191</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6549</v>
+        <v>-0.9652999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.8991</v>
+        <v>-2.8992</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2442</v>
+        <v>1.9338</v>
       </c>
       <c r="V23" t="n">
         <v>-5.8954</v>
